--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T09:56:58+00:00</t>
+    <t>2026-02-06T10:49:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Observation|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Observation</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -670,7 +670,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-observation-type|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-observation-type</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -694,7 +694,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|2.2.0-ballot|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins)
 </t>
   </si>
   <si>
@@ -879,7 +879,7 @@
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-motorisation-cisis|20250624152100</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-motorisation-cisis</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7
@@ -1745,7 +1745,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="150.68359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="131.66796875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1760,7 +1760,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="69.3359375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.828125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T10:49:33+00:00</t>
+    <t>2026-02-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -664,6 +664,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-observation-type"/&gt;
     &lt;code value="MOBILITE"/&gt;
     &lt;display value="Mobilité"/&gt;
   &lt;/coding&gt;
@@ -879,7 +880,7 @@
     <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-type-motorisation-cisis</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-mode-de-transport-cisis</t>
   </si>
   <si>
     <t xml:space="preserve">obs-7

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-observation-mobilite.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T10:00:25+00:00</t>
+    <t>2026-02-11T15:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
